--- a/artfynd/A 58262-2025 artfynd.xlsx
+++ b/artfynd/A 58262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1681,6 +1681,112 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130828624</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Avvakkotunturi, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>756005</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7485851</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Adam Helleberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58262-2025 artfynd.xlsx
+++ b/artfynd/A 58262-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>130828624</v>
       </c>
       <c r="B11" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 58262-2025 artfynd.xlsx
+++ b/artfynd/A 58262-2025 artfynd.xlsx
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56016274</v>
+        <v>130828624</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Avakkotunturi, Lu lm</t>
+          <t>Avvakkotunturi, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755668.1476389883</v>
+        <v>756005</v>
       </c>
       <c r="R2" t="n">
-        <v>7486223.000258154</v>
+        <v>7485851</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +757,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sture Westerberg, Frédéric Forsmark, Emilia Vesterberg</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56016278</v>
+        <v>91821370</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Avakkotunturi, Lu lm</t>
+          <t>Avvakkotunturi, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755668.1476389883</v>
+        <v>756005</v>
       </c>
       <c r="R3" t="n">
-        <v>7486223.000258154</v>
+        <v>7485848</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +871,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sture Westerberg, Frédéric Forsmark, Emilia Vesterberg</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56016276</v>
+        <v>56016272</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755668.1476389883</v>
+        <v>755668</v>
       </c>
       <c r="R4" t="n">
-        <v>7486223.000258154</v>
+        <v>7486223</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,19 +946,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56016273</v>
+        <v>56016275</v>
       </c>
       <c r="B5" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1588</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755668.1476389883</v>
+        <v>755668</v>
       </c>
       <c r="R5" t="n">
-        <v>7486223.000258154</v>
+        <v>7486223</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1084,19 +1043,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1072,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56016275</v>
+        <v>56016274</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755668.1476389883</v>
+        <v>755668</v>
       </c>
       <c r="R6" t="n">
-        <v>7486223.000258154</v>
+        <v>7486223</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1196,19 +1140,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56016272</v>
+        <v>56016273</v>
       </c>
       <c r="B7" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1588</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755668.1476389883</v>
+        <v>755668</v>
       </c>
       <c r="R7" t="n">
-        <v>7486223.000258154</v>
+        <v>7486223</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1308,19 +1237,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,53 +1266,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91821370</v>
+        <v>56016278</v>
       </c>
       <c r="B8" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Avvakkotunturi, Lu lm</t>
+          <t>Avakkotunturi, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>756005.1576427671</v>
+        <v>755668</v>
       </c>
       <c r="R8" t="n">
-        <v>7485848.100068783</v>
+        <v>7486223</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1331,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1356,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
+          <t>Sture Westerberg, Frédéric Forsmark, Emilia Vesterberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91820634</v>
+        <v>56016276</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,17 +1394,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Avvakkotunturi, Lu lm</t>
+          <t>Avakkotunturi, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>756193.9564896668</v>
+        <v>755668</v>
       </c>
       <c r="R9" t="n">
-        <v>7486068.896677304</v>
+        <v>7486223</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1428,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,22 +1453,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
+          <t>Sture Westerberg, Frédéric Forsmark, Emilia Vesterberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91821382</v>
+        <v>91820634</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>755878.1926885757</v>
+        <v>756194</v>
       </c>
       <c r="R10" t="n">
-        <v>7485886.194030315</v>
+        <v>7486069</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1528,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,51 +1557,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130828624</v>
+        <v>56016271</v>
       </c>
       <c r="B11" t="n">
-        <v>92022</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Avvakkotunturi, Lu lm</t>
+          <t>Avakkotunturi, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>756005</v>
+        <v>755589</v>
       </c>
       <c r="R11" t="n">
-        <v>7485851</v>
+        <v>7485975</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1751,12 +1622,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2015-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2015-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,24 +1636,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
+          <t>Sture Westerberg, Frédéric Forsmark, Emilia Vesterberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 58262-2025 artfynd.xlsx
+++ b/artfynd/A 58262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016272</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016275</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016274</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016273</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016278</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016276</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016271</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130828624</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91821370</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,8 +1701,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>